--- a/artfynd/A 10943-2026 artfynd.xlsx
+++ b/artfynd/A 10943-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54548230</v>
+        <v>61381657</v>
       </c>
       <c r="B2" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636494.2339522125</v>
+        <v>636477</v>
       </c>
       <c r="R2" t="n">
-        <v>6556203.844477821</v>
+        <v>6556234</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,27 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På lodyta.</t>
+          <t>På gammal rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +762,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -798,55 +780,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54548193</v>
+        <v>73746045</v>
       </c>
       <c r="B3" t="n">
-        <v>73690</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>311</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636447.8467408074</v>
+        <v>636476</v>
       </c>
       <c r="R3" t="n">
-        <v>6556320.87101217</v>
+        <v>6556090</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,27 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammal ek.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,55 +862,51 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73738378</v>
+        <v>73746220</v>
       </c>
       <c r="B4" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>93</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ekpricklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Inoderma byssaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Weigel) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,14 +914,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NV Yngsviken, Sjundaskogen, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636446.928681728</v>
+        <v>636482</v>
       </c>
       <c r="R4" t="n">
-        <v>6556317.755548824</v>
+        <v>6556212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,44 +974,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73738379</v>
+        <v>73738373</v>
       </c>
       <c r="B5" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,14 +1014,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NV Yngsviken, Sjundaskogen, Srm</t>
+          <t>NO Sarvsjön, Sjundaskogen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636446.928681728</v>
+        <v>636326</v>
       </c>
       <c r="R5" t="n">
-        <v>6556317.755548824</v>
+        <v>6556334</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,19 +1051,9 @@
           <t>2018-10-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,12 +1084,7 @@
         <v>73738380</v>
       </c>
       <c r="B6" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636446.928681728</v>
+        <v>636447</v>
       </c>
       <c r="R6" t="n">
-        <v>6556317.755548824</v>
+        <v>6556318</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,19 +1151,9 @@
           <t>2018-10-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,37 +1181,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73746220</v>
+        <v>73746197</v>
       </c>
       <c r="B7" t="n">
-        <v>73521</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>93</v>
+        <v>309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ekpricklav</t>
+          <t>Parknål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Inoderma byssaceum</t>
+          <t>Chaenotheca hispidula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weigel) Gray</t>
+          <t>(Ach.) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,14 +1214,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>V yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636482.0990896078</v>
+        <v>636440</v>
       </c>
       <c r="R7" t="n">
-        <v>6556212.145241525</v>
+        <v>6556324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,19 +1251,9 @@
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73746237</v>
+        <v>54548193</v>
       </c>
       <c r="B8" t="n">
-        <v>76862</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6443</v>
+        <v>311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,17 +1314,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636482.0990896078</v>
+        <v>636448</v>
       </c>
       <c r="R8" t="n">
-        <v>6556212.145241525</v>
+        <v>6556321</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,22 +1348,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gammal ek.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,56 +1367,50 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73746214</v>
+        <v>73745942</v>
       </c>
       <c r="B9" t="n">
-        <v>76907</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6436</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636482.0990896078</v>
+        <v>636508</v>
       </c>
       <c r="R9" t="n">
-        <v>6556212.145241525</v>
+        <v>6556165</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,19 +1455,9 @@
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,57 +1485,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73746245</v>
+        <v>61381720</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>655</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Schaeff.) With., nom sanct.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636482.0990896078</v>
+        <v>636482</v>
       </c>
       <c r="R10" t="n">
-        <v>6556212.145241525</v>
+        <v>6556218</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,22 +1560,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På grov ek ca 6-7m över marken. Eken står nära bergbrant och har håligheter med mulm och grov skorpbark.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,12 +1586,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1727,12 +1601,7 @@
         <v>73746234</v>
       </c>
       <c r="B11" t="n">
-        <v>88270</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1766,10 +1635,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636482.0990896078</v>
+        <v>636482</v>
       </c>
       <c r="R11" t="n">
-        <v>6556212.145241525</v>
+        <v>6556212</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,19 +1668,9 @@
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,45 +1698,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127771840</v>
+        <v>73738378</v>
       </c>
       <c r="B12" t="n">
-        <v>96066</v>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sarvsjön, Sarvsjön, Srm</t>
+          <t>NV Yngsviken, Sjundaskogen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636437</v>
+        <v>636447</v>
       </c>
       <c r="R12" t="n">
-        <v>6556122</v>
+        <v>6556318</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,22 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:27</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,21 +1779,1361 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127771840</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96601</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sarvsjön, Sarvsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>636437</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6556122</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Gustaf Eibl</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Gustaf Eibl</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>54548230</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>636494</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6556204</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På lodyta.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>73746002</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>636508</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6556165</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På flera tallar</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>73745944</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>636508</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6556165</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>73738379</v>
+      </c>
+      <c r="B17" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NV Yngsviken, Sjundaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>636447</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6556318</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-10-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-10-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>73746196</v>
+      </c>
+      <c r="B18" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>V yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>636440</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6556324</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>73746214</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>636482</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6556212</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>73738372</v>
+      </c>
+      <c r="B20" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO Sarvsjön, Sjundaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>636326</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6556334</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2018-10-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2018-10-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På ek</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>73746237</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>636482</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6556212</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>73746008</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>636508</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6556165</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>54548265</v>
+      </c>
+      <c r="B23" t="n">
+        <v>9363</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>101254</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skeppsvarvsfluga</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lymexylon navale</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>636495</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6556215</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gamla kläckhål på gammal grov ek med håligheter och mulm. Nära bergbrant.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>54548215</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>636486</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6556262</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På litet block.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>73746245</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>636482</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6556212</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10943-2026 artfynd.xlsx
+++ b/artfynd/A 10943-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381657</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746045</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746220</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738373</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738380</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746197</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548193</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73745942</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381720</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,6 +1745,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746234</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738378</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1902,6 +1962,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127771840</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2010,6 +2075,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548230</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2115,6 +2185,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746002</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2215,6 +2290,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73745944</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2315,6 +2395,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738379</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2415,6 +2500,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746196</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2515,6 +2605,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746214</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2620,6 +2715,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738372</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2720,6 +2820,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746237</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2820,6 +2925,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746008</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2931,6 +3041,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548265</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3032,6 +3147,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548215</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3134,8 +3254,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746245</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>